--- a/Luban/Config/Datas/Localization.xlsx
+++ b/Luban/Config/Datas/Localization.xlsx
@@ -4603,6 +4603,222 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pause</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pause</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暂停</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暫停</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUD 右上角暂停按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Game Intro</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Game Intro</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">游戏介绍</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">遊戲介紹</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUD 右上角介绍按钮/弹窗标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back to Level Select</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back to Level Select</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">回到选关</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">回到選關</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">介绍弹窗「回到选关」按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}: drag onto a buildable tile and release to place</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}: drag onto a buildable tile and release to place</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}：拖到可建造格上松手放置，拖回按钮取消</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}：拖到可建造格上鬆手放置，拖回按鈕取消</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拖拽建造提示（占位符 {0} 保留）</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stop the monsters before they reach your base: build towers on the open tiles beside the path.</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stop the monsters before they reach your base: build towers on the open tiles beside the path.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在怪物途经的路边空地建造防御塔，阻止它们抵达你的基地。</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在怪物途經的路邊空地建造防禦塔，阻止它們抵達你的基地。</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">介绍弹窗正文 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Long-press a tower button, drag it onto the board, then release to build.</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Long-press a tower button, drag it onto the board, then release to build.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长按建造栏的塔按钮，拖到棋盘格子上松手即可建造（金币在落地成功后扣除）。</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">長按建造欄的塔按鈕，拖到棋盤格子上鬆手即可建造（金幣在落地成功後扣除）。</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">介绍弹窗正文 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You may slow the monsters down, but never fully block their path.</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You may slow the monsters down, but never fully block their path.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你可以拖慢怪物的脚步，但不能把它们的路完全堵死。</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你可以拖慢怪物的腳步，但不能把它們的路完全堵死。</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">介绍弹窗正文 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Survive every round to win the level.</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Survive every round to win the level.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">撑过全部回合即通关。</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">撐過全部回合即通關。</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">介绍弹窗正文 4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Config/Datas/Localization.xlsx
+++ b/Luban/Config/Datas/Localization.xlsx
@@ -2010,76 +2010,76 @@
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierces a line of enemies</t>
+          <t xml:space="preserve">Normal Tower</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierces a line of enemies</t>
+          <t xml:space="preserve">Normal Tower</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">贯穿一线 · 串排输出</t>
+          <t xml:space="preserve">普通塔</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">貫穿一線 · 串排輸出</t>
+          <t xml:space="preserve">普通塔</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">穿刺塔定位</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hitscan burst · anti-boss</t>
+          <t xml:space="preserve">Blast Tower</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hitscan burst · anti-boss</t>
+          <t xml:space="preserve">Blast Tower</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">激光瞬发 · 点杀精英</t>
+          <t xml:space="preserve">范围塔</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷射瞬發 · 點殺精英</t>
+          <t xml:space="preserve">範圍塔</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">激光塔定位</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal Tower</t>
+          <t xml:space="preserve">Frost Tower</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal Tower</t>
+          <t xml:space="preserve">Frost Tower</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">普通塔</t>
+          <t xml:space="preserve">减速塔</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">普通塔</t>
+          <t xml:space="preserve">減速塔</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2091,22 +2091,22 @@
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blast Tower</t>
+          <t xml:space="preserve">Sell Tower</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blast Tower</t>
+          <t xml:space="preserve">Sell Tower</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">范围塔</t>
+          <t xml:space="preserve">出售确认</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">範圍塔</t>
+          <t xml:space="preserve">出售確認</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2118,49 +2118,53 @@
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frost Tower</t>
+          <t xml:space="preserve">Refund {0}% of total investment.
+This cannot be undone.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frost Tower</t>
+          <t xml:space="preserve">Refund {0}% of total investment.
+This cannot be undone.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">减速塔</t>
+          <t xml:space="preserve">出售后将退回 {0}% 的累计投入
+且无法撤销</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">減速塔</t>
+          <t xml:space="preserve">出售後將退回 {0}% 的累計投入
+且無法撤銷</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierce Tower</t>
+          <t xml:space="preserve">Tower</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierce Tower</t>
+          <t xml:space="preserve">Tower</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">穿刺塔</t>
+          <t xml:space="preserve">塔</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">穿刺塔</t>
+          <t xml:space="preserve">塔</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2172,22 +2176,22 @@
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laser Tower</t>
+          <t xml:space="preserve">You can build on any open ground; paths recompute in real time.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laser Tower</t>
+          <t xml:space="preserve">You can build on any open ground; paths recompute in real time.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">激光塔</t>
+          <t xml:space="preserve">可以在任意空地建塔，路径会实时重算</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷射塔</t>
+          <t xml:space="preserve">可以在任意空地建塔，路徑會即時重算</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2199,22 +2203,22 @@
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sell Tower</t>
+          <t xml:space="preserve">Towers never waste fire when they have no target.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sell Tower</t>
+          <t xml:space="preserve">Towers never waste fire when they have no target.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售确认</t>
+          <t xml:space="preserve">塔没有目标时绝不会浪费火力</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售確認</t>
+          <t xml:space="preserve">塔沒有目標時絕不會浪費火力</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2226,53 +2230,49 @@
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refund {0}% of total investment.
-This cannot be undone.</t>
+          <t xml:space="preserve">Selling a tower refunds part of its total investment.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refund {0}% of total investment.
-This cannot be undone.</t>
+          <t xml:space="preserve">Selling a tower refunds part of its total investment.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售后将退回 {0}% 的累计投入
-且无法撤销</t>
+          <t xml:space="preserve">出售塔可以退回一部分累计投入</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售後將退回 {0}% 的累計投入
-且無法撤銷</t>
+          <t xml:space="preserve">出售塔可以退回一部分累計投入</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower</t>
+          <t xml:space="preserve">Slow towers greatly boost the damage of all nearby towers.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower</t>
+          <t xml:space="preserve">Slow towers greatly boost the damage of all nearby towers.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">塔</t>
+          <t xml:space="preserve">减速塔能大幅提升周围所有塔的输出</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">塔</t>
+          <t xml:space="preserve">減速塔能大幅提升周圍所有塔的輸出</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2284,22 +2284,22 @@
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">You can build on any open ground; paths recompute in real time.</t>
+          <t xml:space="preserve">Flying enemies ignore ground paths; watch your anti-air coverage.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">You can build on any open ground; paths recompute in real time.</t>
+          <t xml:space="preserve">Flying enemies ignore ground paths; watch your anti-air coverage.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">可以在任意空地建塔，路径会实时重算</t>
+          <t xml:space="preserve">飞行怪会无视地面路径，注意覆盖对空</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">可以在任意空地建塔，路徑會即時重算</t>
+          <t xml:space="preserve">飛行怪會無視地面路徑，注意覆蓋對空</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2311,22 +2311,22 @@
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Towers never waste fire when they have no target.</t>
+          <t xml:space="preserve">There is build time between rounds, but you can start early.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Towers never waste fire when they have no target.</t>
+          <t xml:space="preserve">There is build time between rounds, but you can start early.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">塔没有目标时绝不会浪费火力</t>
+          <t xml:space="preserve">回合之间有布防时间，也可以立即开始</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">塔沒有目標時絕不會浪費火力</t>
+          <t xml:space="preserve">回合之間有佈防時間，也可以立即開始</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -2338,22 +2338,22 @@
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selling a tower refunds part of its total investment.</t>
+          <t xml:space="preserve">Initializing resources...</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selling a tower refunds part of its total investment.</t>
+          <t xml:space="preserve">Initializing resources...</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售塔可以退回一部分累计投入</t>
+          <t xml:space="preserve">正在初始化资源系统...</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售塔可以退回一部分累計投入</t>
+          <t xml:space="preserve">正在初始化資源系統...</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2365,22 +2365,22 @@
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slow towers greatly boost the damage of all nearby towers.</t>
+          <t xml:space="preserve">Resource Update</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slow towers greatly boost the damage of all nearby towers.</t>
+          <t xml:space="preserve">Resource Update</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">减速塔能大幅提升周围所有塔的输出</t>
+          <t xml:space="preserve">资源更新</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">減速塔能大幅提升周圍所有塔的輸出</t>
+          <t xml:space="preserve">資源更新</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -2392,22 +2392,22 @@
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flying enemies ignore ground paths; watch your anti-air coverage.</t>
+          <t xml:space="preserve">Checking for updates...</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flying enemies ignore ground paths; watch your anti-air coverage.</t>
+          <t xml:space="preserve">Checking for updates...</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞行怪会无视地面路径，注意覆盖对空</t>
+          <t xml:space="preserve">正在检查更新...</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">飛行怪會無視地面路徑，注意覆蓋對空</t>
+          <t xml:space="preserve">正在檢查更新...</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -2419,22 +2419,22 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is build time between rounds, but you can start early.</t>
+          <t xml:space="preserve">Comparing resource versions...</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is build time between rounds, but you can start early.</t>
+          <t xml:space="preserve">Comparing resource versions...</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合之间有布防时间，也可以立即开始</t>
+          <t xml:space="preserve">正在比对资源版本...</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合之間有佈防時間，也可以立即開始</t>
+          <t xml:space="preserve">正在比對資源版本...</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2446,22 +2446,22 @@
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierce towers can hit a whole column of enemies at once.</t>
+          <t xml:space="preserve">Loading resource manifest...</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierce towers can hit a whole column of enemies at once.</t>
+          <t xml:space="preserve">Loading resource manifest...</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">穿透塔能一次打穿一整列敌人</t>
+          <t xml:space="preserve">正在加载资源清单...</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">穿透塔能一次打穿一整列敵人</t>
+          <t xml:space="preserve">正在載入資源清單...</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2473,22 +2473,22 @@
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initializing resources...</t>
+          <t xml:space="preserve">Resources are up to date</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initializing resources...</t>
+          <t xml:space="preserve">Resources are up to date</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在初始化资源系统...</t>
+          <t xml:space="preserve">资源已是最新</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在初始化資源系統...</t>
+          <t xml:space="preserve">資源已是最新</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2500,22 +2500,22 @@
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resource Update</t>
+          <t xml:space="preserve">Current mode: no resource update needed</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resource Update</t>
+          <t xml:space="preserve">Current mode: no resource update needed</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">资源更新</t>
+          <t xml:space="preserve">当前模式：无需更新资源</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">資源更新</t>
+          <t xml:space="preserve">當前模式：無需更新資源</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2527,22 +2527,22 @@
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checking for updates...</t>
+          <t xml:space="preserve">Editor mode: no resource update needed</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checking for updates...</t>
+          <t xml:space="preserve">Editor mode: no resource update needed</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在检查更新...</t>
+          <t xml:space="preserve">编辑器模式：无需更新资源</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在檢查更新...</t>
+          <t xml:space="preserve">編輯器模式：無需更新資源</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -2554,22 +2554,22 @@
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comparing resource versions...</t>
+          <t xml:space="preserve">Downloading resources...</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comparing resource versions...</t>
+          <t xml:space="preserve">Downloading resources...</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在比对资源版本...</t>
+          <t xml:space="preserve">正在下载资源...</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在比對資源版本...</t>
+          <t xml:space="preserve">正在下載資源...</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2581,103 +2581,103 @@
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loading resource manifest...</t>
+          <t xml:space="preserve">Downloaded {0:F1} MB / {1:F1} MB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loading resource manifest...</t>
+          <t xml:space="preserve">Downloaded {0:F1} MB / {1:F1} MB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在加载资源清单...</t>
+          <t xml:space="preserve">已下载 {0:F1} MB / {1:F1} MB</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在載入資源清單...</t>
+          <t xml:space="preserve">已下載 {0:F1} MB / {1:F1} MB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符保留</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resources are up to date</t>
+          <t xml:space="preserve">Speed {0:F1} MB/s   ETA {1}</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resources are up to date</t>
+          <t xml:space="preserve">Speed {0:F1} MB/s   ETA {1}</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">资源已是最新</t>
+          <t xml:space="preserve">速度 {0:F1} MB/s　剩余约 {1}</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">資源已是最新</t>
+          <t xml:space="preserve">速度 {0:F1} MB/s　剩餘約 {1}</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符保留</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current mode: no resource update needed</t>
+          <t xml:space="preserve">Files {0}/{1}   Failed 0</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current mode: no resource update needed</t>
+          <t xml:space="preserve">Files {0}/{1}   Failed 0</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">当前模式：无需更新资源</t>
+          <t xml:space="preserve">文件 {0}/{1}　失败 0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">當前模式：無需更新資源</t>
+          <t xml:space="preserve">檔案 {0}/{1}　失敗 0</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符保留</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editor mode: no resource update needed</t>
+          <t xml:space="preserve">Download failed</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editor mode: no resource update needed</t>
+          <t xml:space="preserve">Download failed</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">编辑器模式：无需更新资源</t>
+          <t xml:space="preserve">下载失败</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">編輯器模式：無需更新資源</t>
+          <t xml:space="preserve">下載失敗</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -2689,130 +2689,130 @@
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downloading resources...</t>
+          <t xml:space="preserve">Download failed: {0}</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downloading resources...</t>
+          <t xml:space="preserve">Download failed: {0}</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在下载资源...</t>
+          <t xml:space="preserve">下载失败：{0}</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在下載資源...</t>
+          <t xml:space="preserve">下載失敗：{0}</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downloaded {0:F1} MB / {1:F1} MB</t>
+          <t xml:space="preserve">Update complete</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downloaded {0:F1} MB / {1:F1} MB</t>
+          <t xml:space="preserve">Update complete</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">已下载 {0:F1} MB / {1:F1} MB</t>
+          <t xml:space="preserve">更新完成</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">已下載 {0:F1} MB / {1:F1} MB</t>
+          <t xml:space="preserve">更新完成</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Speed {0:F1} MB/s   ETA {1}</t>
+          <t xml:space="preserve">Paused</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Speed {0:F1} MB/s   ETA {1}</t>
+          <t xml:space="preserve">Paused</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">速度 {0:F1} MB/s　剩余约 {1}</t>
+          <t xml:space="preserve">已暂停</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">速度 {0:F1} MB/s　剩餘約 {1}</t>
+          <t xml:space="preserve">已暫停</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Files {0}/{1}   Failed 0</t>
+          <t xml:space="preserve">Retry</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Files {0}/{1}   Failed 0</t>
+          <t xml:space="preserve">Retry</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">文件 {0}/{1}　失败 0</t>
+          <t xml:space="preserve">重试</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">檔案 {0}/{1}　失敗 0</t>
+          <t xml:space="preserve">重試</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Download failed</t>
+          <t xml:space="preserve">Continue</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Download failed</t>
+          <t xml:space="preserve">Continue</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">下载失败</t>
+          <t xml:space="preserve">继续</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">下載失敗</t>
+          <t xml:space="preserve">繼續</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -2824,49 +2824,49 @@
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Download failed: {0}</t>
+          <t xml:space="preserve">Clear the previous level first</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Download failed: {0}</t>
+          <t xml:space="preserve">Clear the previous level first</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">下载失败：{0}</t>
+          <t xml:space="preserve">先通关上一关才能解锁</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">下載失敗：{0}</t>
+          <t xml:space="preserve">先通關上一關才能解鎖</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Update complete</t>
+          <t xml:space="preserve">Not enough gold</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Update complete</t>
+          <t xml:space="preserve">Not enough gold</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新完成</t>
+          <t xml:space="preserve">金币不足</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新完成</t>
+          <t xml:space="preserve">金幣不足</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -2878,22 +2878,22 @@
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paused</t>
+          <t xml:space="preserve">Cannot Build Here</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paused</t>
+          <t xml:space="preserve">Cannot Build Here</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">已暂停</t>
+          <t xml:space="preserve">此处无法建塔</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">已暫停</t>
+          <t xml:space="preserve">此處無法建塔</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -2905,22 +2905,22 @@
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retry</t>
+          <t xml:space="preserve">Sell is unavailable here</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retry</t>
+          <t xml:space="preserve">Sell is unavailable here</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">重试</t>
+          <t xml:space="preserve">出售确认界面不可用</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">重試</t>
+          <t xml:space="preserve">出售確認介面不可用</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -2932,103 +2932,103 @@
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continue</t>
+          <t xml:space="preserve">Next Round ({0})</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continue</t>
+          <t xml:space="preserve">Next Round ({0})</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">继续</t>
+          <t xml:space="preserve">下一回合({0})</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">繼續</t>
+          <t xml:space="preserve">下一回合({0})</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clear the previous level first</t>
+          <t xml:space="preserve">Select Level</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clear the previous level first</t>
+          <t xml:space="preserve">Select Level</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">先通关上一关才能解锁</t>
+          <t xml:space="preserve">选择关卡</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">先通關上一關才能解鎖</t>
+          <t xml:space="preserve">選擇關卡</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">选关界面标题</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not enough gold</t>
+          <t xml:space="preserve">Cleared &lt;color=#E8F0FA&gt;{0}/{1}&lt;/color&gt;　&lt;color=#FFC94D&gt;★ {2}/{3}&lt;/color&gt;</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not enough gold</t>
+          <t xml:space="preserve">Cleared &lt;color=#E8F0FA&gt;{0}/{1}&lt;/color&gt;　&lt;color=#FFC94D&gt;★ {2}/{3}&lt;/color&gt;</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">金币不足</t>
+          <t xml:space="preserve">已通关 &lt;color=#E8F0FA&gt;{0}/{1}&lt;/color&gt;　&lt;color=#FFC94D&gt;★ {2}/{3}&lt;/color&gt;</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣不足</t>
+          <t xml:space="preserve">已通關 &lt;color=#E8F0FA&gt;{0}/{1}&lt;/color&gt;　&lt;color=#FFC94D&gt;★ {2}/{3}&lt;/color&gt;</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">富文本模板，占位符保留</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cannot Build Here</t>
+          <t xml:space="preserve">Locked</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cannot Build Here</t>
+          <t xml:space="preserve">Locked</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">此处无法建塔</t>
+          <t xml:space="preserve">未解锁</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">此處無法建塔</t>
+          <t xml:space="preserve">未解鎖</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3040,130 +3040,130 @@
     <row r="111">
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sell is unavailable here</t>
+          <t xml:space="preserve">Difficulty I</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sell is unavailable here</t>
+          <t xml:space="preserve">Difficulty I</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售确认界面不可用</t>
+          <t xml:space="preserve">难度 Ⅰ</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售確認介面不可用</t>
+          <t xml:space="preserve">難度 Ⅰ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">罗马数字保留</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Next Round ({0})</t>
+          <t xml:space="preserve">Difficulty II</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Next Round ({0})</t>
+          <t xml:space="preserve">Difficulty II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">下一回合({0})</t>
+          <t xml:space="preserve">难度 Ⅱ</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">下一回合({0})</t>
+          <t xml:space="preserve">難度 Ⅱ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve">罗马数字保留</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Select Level</t>
+          <t xml:space="preserve">Difficulty III</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Select Level</t>
+          <t xml:space="preserve">Difficulty III</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">选择关卡</t>
+          <t xml:space="preserve">难度 Ⅲ</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">選擇關卡</t>
+          <t xml:space="preserve">難度 Ⅲ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">选关界面标题</t>
+          <t xml:space="preserve">罗马数字保留</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleared &lt;color=#E8F0FA&gt;{0}/{1}&lt;/color&gt;　&lt;color=#FFC94D&gt;★ {2}/{3}&lt;/color&gt;</t>
+          <t xml:space="preserve">Not Buildable Here</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleared &lt;color=#E8F0FA&gt;{0}/{1}&lt;/color&gt;　&lt;color=#FFC94D&gt;★ {2}/{3}&lt;/color&gt;</t>
+          <t xml:space="preserve">Not Buildable Here</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">已通关 &lt;color=#E8F0FA&gt;{0}/{1}&lt;/color&gt;　&lt;color=#FFC94D&gt;★ {2}/{3}&lt;/color&gt;</t>
+          <t xml:space="preserve">该位置不可建造</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">已通關 &lt;color=#E8F0FA&gt;{0}/{1}&lt;/color&gt;　&lt;color=#FFC94D&gt;★ {2}/{3}&lt;/color&gt;</t>
+          <t xml:space="preserve">該位置不可建造</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">富文本模板，占位符保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Locked</t>
+          <t xml:space="preserve">Tower already there</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Locked</t>
+          <t xml:space="preserve">Tower already there</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">未解锁</t>
+          <t xml:space="preserve">该位置已有防御塔</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">未解鎖</t>
+          <t xml:space="preserve">該位置已有防禦塔</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3175,130 +3175,130 @@
     <row r="116">
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Difficulty I</t>
+          <t xml:space="preserve">Cannot fully block the path</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Difficulty I</t>
+          <t xml:space="preserve">Cannot fully block the path</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">难度 Ⅰ</t>
+          <t xml:space="preserve">不能完全阻断怪物路径</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">難度 Ⅰ</t>
+          <t xml:space="preserve">不能完全阻斷怪物路徑</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">罗马数字保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Difficulty II</t>
+          <t xml:space="preserve">Not enough gold, need {0}</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Difficulty II</t>
+          <t xml:space="preserve">Not enough gold, need {0}</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">难度 Ⅱ</t>
+          <t xml:space="preserve">金币不足，需要 {0}</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">難度 Ⅱ</t>
+          <t xml:space="preserve">金幣不足，需要 {0}</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">罗马数字保留</t>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Difficulty III</t>
+          <t xml:space="preserve">{0}: move to a buildable tile and click to place, right-click/ESC to cancel</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Difficulty III</t>
+          <t xml:space="preserve">{0}: move to a buildable tile and click to place, right-click/ESC to cancel</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">难度 Ⅲ</t>
+          <t xml:space="preserve">{0}：移动到可建造格上点击放置，右键/ESC 取消</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">難度 Ⅲ</t>
+          <t xml:space="preserve">{0}：移動到可建造格上點擊放置，右鍵/ESC 取消</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">罗马数字保留</t>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Buildable Here</t>
+          <t xml:space="preserve">No tower config for type={0} level={1}</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Buildable Here</t>
+          <t xml:space="preserve">No tower config for type={0} level={1}</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">该位置不可建造</t>
+          <t xml:space="preserve">找不到 type={0} level={1} 的塔配置</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">該位置不可建造</t>
+          <t xml:space="preserve">找不到 type={0} level={1} 的塔配置</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符保留</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower already there</t>
+          <t xml:space="preserve">No Tile Here</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower already there</t>
+          <t xml:space="preserve">No Tile Here</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">该位置已有防御塔</t>
+          <t xml:space="preserve">该位置无法建造</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">該位置已有防禦塔</t>
+          <t xml:space="preserve">該位置無法建造</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -3310,22 +3310,22 @@
     <row r="121">
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cannot fully block the path</t>
+          <t xml:space="preserve">An enemy is on this tile, try another spot</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cannot fully block the path</t>
+          <t xml:space="preserve">An enemy is on this tile, try another spot</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">不能完全阻断怪物路径</t>
+          <t xml:space="preserve">该格上正有怪物，换个位置吧</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">不能完全阻斷怪物路徑</t>
+          <t xml:space="preserve">該格上正有怪物，換個位置吧</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -3337,103 +3337,103 @@
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not enough gold, need {0}</t>
+          <t xml:space="preserve">Failed to load tower asset</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not enough gold, need {0}</t>
+          <t xml:space="preserve">Failed to load tower asset</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">金币不足，需要 {0}</t>
+          <t xml:space="preserve">防御塔资源加载失败</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣不足，需要 {0}</t>
+          <t xml:space="preserve">防禦塔資源載入失敗</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}: move to a buildable tile and click to place, right-click/ESC to cancel</t>
+          <t xml:space="preserve">Tower is already at max level</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}: move to a buildable tile and click to place, right-click/ESC to cancel</t>
+          <t xml:space="preserve">Tower is already at max level</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}：移动到可建造格上点击放置，右键/ESC 取消</t>
+          <t xml:space="preserve">该防御塔已满级</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}：移動到可建造格上點擊放置，右鍵/ESC 取消</t>
+          <t xml:space="preserve">該防禦塔已滿級</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">No tower config for type={0} level={1}</t>
+          <t xml:space="preserve">No next-level config available</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">No tower config for type={0} level={1}</t>
+          <t xml:space="preserve">No next-level config available</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">找不到 type={0} level={1} 的塔配置</t>
+          <t xml:space="preserve">该防御塔暂无可升级的下一级配置</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">找不到 type={0} level={1} 的塔配置</t>
+          <t xml:space="preserve">該防禦塔暫無可升級的下一級配置</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Tile Here</t>
+          <t xml:space="preserve">Tower is not on a tile, cannot upgrade</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Tile Here</t>
+          <t xml:space="preserve">Tower is not on a tile, cannot upgrade</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">该位置无法建造</t>
+          <t xml:space="preserve">该防御塔不在格子上，无法升级</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">該位置無法建造</t>
+          <t xml:space="preserve">該防禦塔不在格子上，無法升級</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -3445,49 +3445,49 @@
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">An enemy is on this tile, try another spot</t>
+          <t xml:space="preserve">Not enough gold, upgrade needs {0}</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">An enemy is on this tile, try another spot</t>
+          <t xml:space="preserve">Not enough gold, upgrade needs {0}</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">该格上正有怪物，换个位置吧</t>
+          <t xml:space="preserve">金币不足，升级需要 {0}</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">該格上正有怪物，換個位置吧</t>
+          <t xml:space="preserve">金幣不足，升級需要 {0}</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failed to load tower asset</t>
+          <t xml:space="preserve">Upgrade failed: tower asset missing, gold refunded</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failed to load tower asset</t>
+          <t xml:space="preserve">Upgrade failed: tower asset missing, gold refunded</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">防御塔资源加载失败</t>
+          <t xml:space="preserve">升级失败：防御塔资源加载失败，已退还金币</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">防禦塔資源載入失敗</t>
+          <t xml:space="preserve">升級失敗：防禦塔資源載入失敗，已退還金幣</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -3499,130 +3499,130 @@
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower is already at max level</t>
+          <t xml:space="preserve">Upgraded to {0} Lv.{1}</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower is already at max level</t>
+          <t xml:space="preserve">Upgraded to {0} Lv.{1}</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">该防御塔已满级</t>
+          <t xml:space="preserve">已升级为 {0} Lv.{1}</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">該防禦塔已滿級</t>
+          <t xml:space="preserve">已升級為 {0} Lv.{1}</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符保留</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">No next-level config available</t>
+          <t xml:space="preserve">Tower sold, refunded {0} gold</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">No next-level config available</t>
+          <t xml:space="preserve">Tower sold, refunded {0} gold</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">该防御塔暂无可升级的下一级配置</t>
+          <t xml:space="preserve">已出售防御塔，返还 {0} 金币</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">該防禦塔暫無可升級的下一級配置</t>
+          <t xml:space="preserve">已出售防禦塔，返還 {0} 金幣</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower is not on a tile, cannot upgrade</t>
+          <t xml:space="preserve">&lt;color=#9FB3C8&gt;Best&lt;/color&gt; {0}</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower is not on a tile, cannot upgrade</t>
+          <t xml:space="preserve">&lt;color=#9FB3C8&gt;Best&lt;/color&gt; {0}</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">该防御塔不在格子上，无法升级</t>
+          <t xml:space="preserve">&lt;color=#9FB3C8&gt;历史最高&lt;/color&gt; {0}</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">該防禦塔不在格子上，無法升級</t>
+          <t xml:space="preserve">&lt;color=#9FB3C8&gt;歷史最高&lt;/color&gt; {0}</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">富文本模板，占位符保留</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not enough gold, upgrade needs {0}</t>
+          <t xml:space="preserve">Config load failed, see Console</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not enough gold, upgrade needs {0}</t>
+          <t xml:space="preserve">Config load failed, see Console</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">金币不足，升级需要 {0}</t>
+          <t xml:space="preserve">配置表加载失败，请查看 Console</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣不足，升級需要 {0}</t>
+          <t xml:space="preserve">配置表載入失敗，請查看 Console</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upgrade failed: tower asset missing, gold refunded</t>
+          <t xml:space="preserve">Monster codex: UI not ready yet</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upgrade failed: tower asset missing, gold refunded</t>
+          <t xml:space="preserve">Monster codex: UI not ready yet</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">升级失败：防御塔资源加载失败，已退还金币</t>
+          <t xml:space="preserve">怪物图鉴：界面生成中</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">升級失敗：防禦塔資源載入失敗，已退還金幣</t>
+          <t xml:space="preserve">怪物圖鑑：介面生成中</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -3634,49 +3634,49 @@
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upgraded to {0} Lv.{1}</t>
+          <t xml:space="preserve">Level config incomplete</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upgraded to {0} Lv.{1}</t>
+          <t xml:space="preserve">Level config incomplete</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">已升级为 {0} Lv.{1}</t>
+          <t xml:space="preserve">关卡配置不完整</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">已升級為 {0} Lv.{1}</t>
+          <t xml:space="preserve">關卡配置不完整</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower sold, refunded {0} gold</t>
+          <t xml:space="preserve">Level ready: {0}, click Start to fight</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower sold, refunded {0} gold</t>
+          <t xml:space="preserve">Level ready: {0}, click Start to fight</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">已出售防御塔，返还 {0} 金币</t>
+          <t xml:space="preserve">关卡就绪：{0}，点击「开始」迎战</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">已出售防禦塔，返還 {0} 金幣</t>
+          <t xml:space="preserve">關卡就緒：{0}，點擊「開始」迎戰</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -3688,49 +3688,49 @@
     <row r="135">
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;color=#9FB3C8&gt;Best&lt;/color&gt; {0}</t>
+          <t xml:space="preserve">Round in progress, wait for it to finish</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;color=#9FB3C8&gt;Best&lt;/color&gt; {0}</t>
+          <t xml:space="preserve">Round in progress, wait for it to finish</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;color=#9FB3C8&gt;历史最高&lt;/color&gt; {0}</t>
+          <t xml:space="preserve">回合进行中，请等待本回合结束</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;color=#9FB3C8&gt;歷史最高&lt;/color&gt; {0}</t>
+          <t xml:space="preserve">回合進行中，請等待本回合結束</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">富文本模板，占位符保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Config load failed, see Console</t>
+          <t xml:space="preserve">Game already ended</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Config load failed, see Console</t>
+          <t xml:space="preserve">Game already ended</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">配置表加载失败，请查看 Console</t>
+          <t xml:space="preserve">本局已结束</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">配置表載入失敗，請查看 Console</t>
+          <t xml:space="preserve">本局已結束</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -3742,76 +3742,76 @@
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monster codex: UI not ready yet</t>
+          <t xml:space="preserve">Round {0} config missing</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monster codex: UI not ready yet</t>
+          <t xml:space="preserve">Round {0} config missing</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">怪物图鉴：界面生成中</t>
+          <t xml:space="preserve">回合 {0} 配置缺失</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">怪物圖鑑：介面生成中</t>
+          <t xml:space="preserve">回合 {0} 配置缺失</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level config incomplete</t>
+          <t xml:space="preserve">Round {0}/{1} start</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level config incomplete</t>
+          <t xml:space="preserve">Round {0}/{1} start</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡配置不完整</t>
+          <t xml:space="preserve">回合 {0}/{1} 开始</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">關卡配置不完整</t>
+          <t xml:space="preserve">回合 {0}/{1} 開始</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符保留</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level ready: {0}, click Start to fight</t>
+          <t xml:space="preserve">Round reward +{0} gold</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level ready: {0}, click Start to fight</t>
+          <t xml:space="preserve">Round reward +{0} gold</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡就绪：{0}，点击「开始」迎战</t>
+          <t xml:space="preserve">回合奖励 +{0} 金币</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">關卡就緒：{0}，點擊「開始」迎戰</t>
+          <t xml:space="preserve">回合獎勵 +{0} 金幣</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -3823,130 +3823,130 @@
     <row r="140">
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round in progress, wait for it to finish</t>
+          <t xml:space="preserve">Cleared! Earned {0}</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round in progress, wait for it to finish</t>
+          <t xml:space="preserve">Cleared! Earned {0}</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合进行中，请等待本回合结束</t>
+          <t xml:space="preserve">通关！获得 {0}</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合進行中，請等待本回合結束</t>
+          <t xml:space="preserve">通關！獲得 {0}</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Game already ended</t>
+          <t xml:space="preserve">Round complete, next round starts in {0}s (or tap Next Round)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Game already ended</t>
+          <t xml:space="preserve">Round complete, next round starts in {0}s (or tap Next Round)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">本局已结束</t>
+          <t xml:space="preserve">回合完成，{0} 秒后自动开始下一回合（也可直接点「下一回合」）</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">本局已結束</t>
+          <t xml:space="preserve">回合完成，{0} 秒後自動開始下一回合（也可直接點「下一回合」）</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">占位符 {0} 保留</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round {0} config missing</t>
+          <t xml:space="preserve">Congratulations!</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round {0} config missing</t>
+          <t xml:space="preserve">Congratulations!</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合 {0} 配置缺失</t>
+          <t xml:space="preserve">恭喜通关！</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合 {0} 配置缺失</t>
+          <t xml:space="preserve">恭喜通關！</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round {0}/{1} start</t>
+          <t xml:space="preserve">Defense failed...</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round {0}/{1} start</t>
+          <t xml:space="preserve">Defense failed...</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合 {0}/{1} 开始</t>
+          <t xml:space="preserve">防御失败……</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合 {0}/{1} 開始</t>
+          <t xml:space="preserve">防禦失敗……</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round reward +{0} gold</t>
+          <t xml:space="preserve">Resumed from last progress (next round: {0})</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round reward +{0} gold</t>
+          <t xml:space="preserve">Resumed from last progress (next round: {0})</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合奖励 +{0} 金币</t>
+          <t xml:space="preserve">已从上次进度继续（下一回合：第 {0} 回合）</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合獎勵 +{0} 金幣</t>
+          <t xml:space="preserve">已從上次進度繼續（下一回合：第 {0} 回合）</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -3958,22 +3958,22 @@
     <row r="145">
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleared! Earned {0}</t>
+          <t xml:space="preserve">Entering level {0}...</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleared! Earned {0}</t>
+          <t xml:space="preserve">Entering level {0}...</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">通关！获得 {0}</t>
+          <t xml:space="preserve">正在进入第 {0} 关...</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">通關！獲得 {0}</t>
+          <t xml:space="preserve">正在進入第 {0} 關...</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -3985,49 +3985,49 @@
     <row r="146">
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round complete, next round starts in {0}s (or tap Next Round)</t>
+          <t xml:space="preserve">Tower panel not ready, cannot upgrade/sell yet</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round complete, next round starts in {0}s (or tap Next Round)</t>
+          <t xml:space="preserve">Tower panel not ready, cannot upgrade/sell yet</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合完成，{0} 秒后自动开始下一回合（也可直接点「下一回合」）</t>
+          <t xml:space="preserve">塔操作面板资源未就绪，暂无法升级/出售（补齐 TowerInfoView 后可用）</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">回合完成，{0} 秒後自動開始下一回合（也可直接點「下一回合」）</t>
+          <t xml:space="preserve">塔操作面板資源未就緒，暫無法升級/出售（補齊 TowerInfoView 後可用）</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations!</t>
+          <t xml:space="preserve">Resource init failed, see Console</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations!</t>
+          <t xml:space="preserve">Resource init failed, see Console</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">恭喜通关！</t>
+          <t xml:space="preserve">资源系统初始化失败，请查看 Console</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">恭喜通關！</t>
+          <t xml:space="preserve">資源系統初始化失敗，請查看 Console</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -4039,22 +4039,22 @@
     <row r="148">
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Defense failed...</t>
+          <t xml:space="preserve">Loading config...</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Defense failed...</t>
+          <t xml:space="preserve">Loading config...</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">防御失败……</t>
+          <t xml:space="preserve">正在加载配置表...</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">防禦失敗……</t>
+          <t xml:space="preserve">正在載入配置表...</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -4066,754 +4066,619 @@
     <row r="149">
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resumed from last progress (next round: {0})</t>
+          <t xml:space="preserve">Preparing level data...</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resumed from last progress (next round: {0})</t>
+          <t xml:space="preserve">Preparing level data...</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">已从上次进度继续（下一回合：第 {0} 回合）</t>
+          <t xml:space="preserve">正在准备关卡数据...</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">已從上次進度繼續（下一回合：第 {0} 回合）</t>
+          <t xml:space="preserve">正在準備關卡資料...</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entering level {0}...</t>
+          <t xml:space="preserve">Ready</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entering level {0}...</t>
+          <t xml:space="preserve">Ready</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在进入第 {0} 关...</t>
+          <t xml:space="preserve">准备完成</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在進入第 {0} 關...</t>
+          <t xml:space="preserve">準備完成</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">占位符 {0} 保留</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower panel not ready, cannot upgrade/sell yet</t>
+          <t xml:space="preserve">Confirm</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower panel not ready, cannot upgrade/sell yet</t>
+          <t xml:space="preserve">Confirm</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">塔操作面板资源未就绪，暂无法升级/出售（补齐 TowerInfoView 后可用）</t>
+          <t xml:space="preserve">确认</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">塔操作面板資源未就緒，暫無法升級/出售（補齊 TowerInfoView 後可用）</t>
+          <t xml:space="preserve">確認</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">通用确认标题</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resource init failed, see Console</t>
+          <t xml:space="preserve">Confirm Sell</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resource init failed, see Console</t>
+          <t xml:space="preserve">Confirm Sell</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">资源系统初始化失败，请查看 Console</t>
+          <t xml:space="preserve">确认出售</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">資源系統初始化失敗，請查看 Console</t>
+          <t xml:space="preserve">確認出售</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">出售确认按钮</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loading config...</t>
+          <t xml:space="preserve">Sell this tower?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loading config...</t>
+          <t xml:space="preserve">Sell this tower?</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在加载配置表...</t>
+          <t xml:space="preserve">确认出售？</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在載入配置表...</t>
+          <t xml:space="preserve">確認出售？</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">出售确认标题</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preparing level data...</t>
+          <t xml:space="preserve">Refund</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preparing level data...</t>
+          <t xml:space="preserve">Refund</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在准备关卡数据...</t>
+          <t xml:space="preserve">退回金币</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">正在準備關卡資料...</t>
+          <t xml:space="preserve">退回金幣</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">出售确认退回标签</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ready</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ready</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">准备完成</t>
+          <t xml:space="preserve">关闭</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">準備完成</t>
+          <t xml:space="preserve">關閉</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">通用关闭按钮</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm</t>
+          <t xml:space="preserve">Sell</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm</t>
+          <t xml:space="preserve">Sell</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">确认</t>
+          <t xml:space="preserve">出售</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">確認</t>
+          <t xml:space="preserve">出售</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">通用确认标题</t>
+          <t xml:space="preserve">塔面板出售按钮</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm Sell</t>
+          <t xml:space="preserve">Upgrade</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm Sell</t>
+          <t xml:space="preserve">Upgrade</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">确认出售</t>
+          <t xml:space="preserve">升级</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">確認出售</t>
+          <t xml:space="preserve">升級</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售确认按钮</t>
+          <t xml:space="preserve">塔面板升级按钮</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sell this tower?</t>
+          <t xml:space="preserve">Restart Level</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sell this tower?</t>
+          <t xml:space="preserve">Restart Level</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">确认出售？</t>
+          <t xml:space="preserve">重新开始本关</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">確認出售？</t>
+          <t xml:space="preserve">重新開始本關</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售确认标题</t>
+          <t xml:space="preserve">暂停界面重开</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refund</t>
+          <t xml:space="preserve">Volume +</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refund</t>
+          <t xml:space="preserve">Volume +</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">退回金币</t>
+          <t xml:space="preserve">音量 ＋</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">退回金幣</t>
+          <t xml:space="preserve">音量 ＋</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售确认退回标签</t>
+          <t xml:space="preserve">设置音量加</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Volume -</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Volume -</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">关闭</t>
+          <t xml:space="preserve">音量 −</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">關閉</t>
+          <t xml:space="preserve">音量 −</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">通用关闭按钮</t>
+          <t xml:space="preserve">设置音量减</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sell</t>
+          <t xml:space="preserve">Tower Codex</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sell</t>
+          <t xml:space="preserve">Tower Codex</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售</t>
+          <t xml:space="preserve">防御塔图鉴</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">出售</t>
+          <t xml:space="preserve">防禦塔圖鑑</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">塔面板出售按钮</t>
+          <t xml:space="preserve">图鉴页标题</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upgrade</t>
+          <t xml:space="preserve">Level</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upgrade</t>
+          <t xml:space="preserve">Level</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">升级</t>
+          <t xml:space="preserve">关卡</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">升級</t>
+          <t xml:space="preserve">關卡</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">塔面板升级按钮</t>
+          <t xml:space="preserve">选关卡片/详情页默认标签</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Restart Level</t>
+          <t xml:space="preserve">FREEDOM TOWER · Tower Defense</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Restart Level</t>
+          <t xml:space="preserve">FREEDOM TOWER · Tower Defense</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">重新开始本关</t>
+          <t xml:space="preserve">自由人塔防 · 单机塔防</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">重新開始本關</t>
+          <t xml:space="preserve">自由人塔防 · 單機塔防</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂停界面重开</t>
+          <t xml:space="preserve">主菜单/开屏副标题</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volume +</t>
+          <t xml:space="preserve">Pause</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volume +</t>
+          <t xml:space="preserve">Pause</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">音量 ＋</t>
+          <t xml:space="preserve">暂停</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">音量 ＋</t>
+          <t xml:space="preserve">暫停</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">设置音量加</t>
+          <t xml:space="preserve">HUD 右上角暂停按钮</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volume -</t>
+          <t xml:space="preserve">Game Intro</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volume -</t>
+          <t xml:space="preserve">Game Intro</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">音量 −</t>
+          <t xml:space="preserve">游戏介绍</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">音量 −</t>
+          <t xml:space="preserve">遊戲介紹</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">设置音量减</t>
+          <t xml:space="preserve">HUD 右上角介绍按钮/弹窗标题</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower Codex</t>
+          <t xml:space="preserve">Back to Level Select</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tower Codex</t>
+          <t xml:space="preserve">Back to Level Select</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">防御塔图鉴</t>
+          <t xml:space="preserve">回到选关</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">防禦塔圖鑑</t>
+          <t xml:space="preserve">回到選關</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">图鉴页标题</t>
+          <t xml:space="preserve">介绍弹窗「回到选关」按钮</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level</t>
+          <t xml:space="preserve">{0}: drag onto a buildable tile and release to place</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level</t>
+          <t xml:space="preserve">{0}: drag onto a buildable tile and release to place</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡</t>
+          <t xml:space="preserve">{0}：拖到可建造格上松手放置，拖回按钮取消</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">關卡</t>
+          <t xml:space="preserve">{0}：拖到可建造格上鬆手放置，拖回按鈕取消</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">选关卡片/详情页默认标签</t>
+          <t xml:space="preserve">拖拽建造提示（占位符 {0} 保留）</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREEDOM TOWER · Tower Defense</t>
+          <t xml:space="preserve">Stop the monsters before they reach your base: build towers on the open tiles beside the path.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREEDOM TOWER · Tower Defense</t>
+          <t xml:space="preserve">Stop the monsters before they reach your base: build towers on the open tiles beside the path.</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">自由人塔防 · 单机塔防</t>
+          <t xml:space="preserve">在怪物途经的路边空地建造防御塔，阻止它们抵达你的基地。</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">自由人塔防 · 單機塔防</t>
+          <t xml:space="preserve">在怪物途經的路邊空地建造防禦塔，阻止它們抵達你的基地。</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">主菜单/开屏副标题</t>
+          <t xml:space="preserve">介绍弹窗正文 1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pause</t>
+          <t xml:space="preserve">Long-press a tower button, drag it onto the board, then release to build.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pause</t>
+          <t xml:space="preserve">Long-press a tower button, drag it onto the board, then release to build.</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">暂停</t>
+          <t xml:space="preserve">长按建造栏的塔按钮，拖到棋盘格子上松手即可建造（金币在落地成功后扣除）。</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">暫停</t>
+          <t xml:space="preserve">長按建造欄的塔按鈕，拖到棋盤格子上鬆手即可建造（金幣在落地成功後扣除）。</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD 右上角暂停按钮</t>
+          <t xml:space="preserve">介绍弹窗正文 2</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Game Intro</t>
+          <t xml:space="preserve">You may slow the monsters down, but never fully block their path.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Game Intro</t>
+          <t xml:space="preserve">You may slow the monsters down, but never fully block their path.</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">游戏介绍</t>
+          <t xml:space="preserve">你可以拖慢怪物的脚步，但不能把它们的路完全堵死。</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">遊戲介紹</t>
+          <t xml:space="preserve">你可以拖慢怪物的腳步，但不能把它們的路完全堵死。</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD 右上角介绍按钮/弹窗标题</t>
+          <t xml:space="preserve">介绍弹窗正文 3</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to Level Select</t>
+          <t xml:space="preserve">Survive every round to win the level.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to Level Select</t>
+          <t xml:space="preserve">Survive every round to win the level.</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">回到选关</t>
+          <t xml:space="preserve">撑过全部回合即通关。</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">回到選關</t>
+          <t xml:space="preserve">撐過全部回合即通關。</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">介绍弹窗「回到选关」按钮</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="B172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{0}: drag onto a buildable tile and release to place</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{0}: drag onto a buildable tile and release to place</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{0}：拖到可建造格上松手放置，拖回按钮取消</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{0}：拖到可建造格上鬆手放置，拖回按鈕取消</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">拖拽建造提示（占位符 {0} 保留）</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="B173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stop the monsters before they reach your base: build towers on the open tiles beside the path.</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stop the monsters before they reach your base: build towers on the open tiles beside the path.</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在怪物途经的路边空地建造防御塔，阻止它们抵达你的基地。</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在怪物途經的路邊空地建造防禦塔，阻止它們抵達你的基地。</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">介绍弹窗正文 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="B174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Long-press a tower button, drag it onto the board, then release to build.</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Long-press a tower button, drag it onto the board, then release to build.</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">长按建造栏的塔按钮，拖到棋盘格子上松手即可建造（金币在落地成功后扣除）。</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">長按建造欄的塔按鈕，拖到棋盤格子上鬆手即可建造（金幣在落地成功後扣除）。</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">介绍弹窗正文 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="B175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You may slow the monsters down, but never fully block their path.</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You may slow the monsters down, but never fully block their path.</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">你可以拖慢怪物的脚步，但不能把它们的路完全堵死。</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">你可以拖慢怪物的腳步，但不能把它們的路完全堵死。</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">介绍弹窗正文 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="B176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Survive every round to win the level.</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Survive every round to win the level.</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">撑过全部回合即通关。</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">撐過全部回合即通關。</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
         <is>
           <t xml:space="preserve">介绍弹窗正文 4</t>
         </is>

--- a/Luban/Config/Datas/Localization.xlsx
+++ b/Luban/Config/Datas/Localization.xlsx
@@ -4684,6 +4684,3327 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AdvancedHen</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AdvancedHen</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高阶母鸡</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高階母雞</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bat</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bat</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蝙蝠</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蝙蝠</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BattlePanther</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BattlePanther</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">战豹</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">戰豹</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bear</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bear</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大熊</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大熊</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BearMounted</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BearMounted</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骑熊</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">騎熊</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BlackBear</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BlackBear</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黑熊</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黑熊</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BlackBoar</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BlackBoar</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黑野猪</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黑野豬</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BlackWolf</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BlackWolf</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黑狼</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黑狼</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BlueScorpion</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BlueScorpion</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蓝蝎</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">藍蠍</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boar</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boar</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">野猪</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">野豬</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BoarMounted</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BoarMounted</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骑猪</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">騎豬</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BugQueen</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BugQueen</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">虫后</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蟲后</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bull</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bull</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公牛</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公牛</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BullMounted</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BullMounted</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骑牛</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">騎牛</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BullyRooster</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BullyRooster</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恶霸公鸡</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">惡霸公雞</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bunny</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bunny</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小兔</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小兔</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Burro</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Burro</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小毛驴</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小毛驢</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Butcher</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Butcher</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠夫</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠夫</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cannibal</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cannibal</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食人族</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食人族</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caterpillar</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caterpillar</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">毛毛虫</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">毛毛蟲</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CaveCaterpillar</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CaveCaterpillar</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">洞穴毛虫</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">洞穴毛蟲</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CaveRat</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CaveRat</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">洞穴鼠</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">洞穴鼠</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerberus</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerberus</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地狱犬</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地獄犬</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chick</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chick</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雏鸡</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雛雞</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chicken</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chicken</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雞</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cow</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cow</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奶牛</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奶牛</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crawler</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crawler</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爬行者</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爬行者</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CrystalLizard</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CrystalLizard</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水晶蜥蜴</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水晶蜥蜴</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DarkBunny</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DarkBunny</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗黑兔</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗黑兔</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Donkey</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Donkey</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">驴</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">驢</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drake</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drake</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幼龙</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幼龍</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DreadEye</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DreadEye</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恐惧之眼</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恐懼之眼</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dreadnought</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dreadnought</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恐惧巨兽</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恐懼巨獸</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duck</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duck</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸭子</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鴨子</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EvilEye</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EvilEye</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">邪眼</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">邪眼</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FancyParasite</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FancyParasite</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华丽寄生体</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">華麗寄生體</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FlyingDemon</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FlyingDemon</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">飞行恶魔</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">飛行惡魔</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ForestTurkey</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ForestTurkey</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">森林火鸡</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">森林火雞</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghost</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghost</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幽灵</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幽靈</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goat</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goat</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山羊</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山羊</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobbler</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobbler</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">贪食火鸡</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪食火雞</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goose</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goose</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大鹅</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大鵝</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GreenParasite</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GreenParasite</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">绿色寄生体</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">綠色寄生體</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GreenScorpion</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GreenScorpion</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">绿蝎</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">綠蠍</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hen</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hen</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">母鸡</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">母雞</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hog</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hog</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大肥猪</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大肥豬</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horse</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horse</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骏马</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">駿馬</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Husky</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Husky</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">哈士奇</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">哈士奇</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IceParasite</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IceParasite</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒冰寄生体</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒冰寄生體</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InfectedRat</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InfectedRat</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">感染鼠</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">感染鼠</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ironclad</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ironclad</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铁甲兽</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鐵甲獸</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juggernaut</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juggernaut</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碾压巨兽</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碾壓巨獸</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Larva</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Larva</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幼虫</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幼蟲</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lion</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lion</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狮子</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">獅子</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LittleBunny</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LittleBunny</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迷你兔</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迷你兔</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maneater</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maneater</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食人兽</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食人獸</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeatBug</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MeatBug</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉虫</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉蟲</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MechanicalParasiteTypeA</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MechanicalParasiteTypeA</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机械寄生体·甲</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機械寄生體·甲</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MechanicalParasiteTypeB</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MechanicalParasiteTypeB</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机械寄生体·乙</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機械寄生體·乙</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mimic</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mimic</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拟态怪</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">擬態怪</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MimicChest</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MimicChest</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宝箱怪</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寶箱怪</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MinerBoar</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MinerBoar</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矿工野猪</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">礦工野豬</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MohawkBat</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MohawkBat</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">莫西干蝙蝠</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">莫西干蝙蝠</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monkey</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monkey</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">猴子</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">猴子</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MosquitoParasite</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MosquitoParasite</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蚊型寄生体</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蚊型寄生體</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MossQueen</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MossQueen</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">苔藓女王</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">苔蘚女王</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MossQueenMounted</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MossQueenMounted</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骑乘苔藓女王</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">騎乘苔蘚女王</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nightmare</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nightmare</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">梦魇</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夢魘</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NormalEnemy</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NormalEnemy</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">普通怪</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">普通怪</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ogre</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ogre</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食人魔</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食人魔</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ox</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ox</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">壮牛</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">壯牛</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panther</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panther</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美洲豹</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美洲豹</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pig</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pig</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">猪</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豬</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piggy</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piggy</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小猪</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小豬</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PirateBoar</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PirateBoar</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海盗野猪</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">海盜野豬</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pony</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pony</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矮脚马</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矮腳馬</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porcupine</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porcupine</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豪猪</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豪豬</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porky</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porky</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">胖猪</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">胖豬</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedBlackBear</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedBlackBear</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夺魂黑熊</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奪魂黑熊</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedBlackBoar</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedBlackBoar</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夺魂黑野猪</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奪魂黑野豬</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedRat</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedRat</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夺魂鼠</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奪魂鼠</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedWarg</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedWarg</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夺魂座狼</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奪魂座狼</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedWatchdog</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedWatchdog</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夺魂看门犬</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奪魂看門犬</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedWolf</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PossessedWolf</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夺魂狼</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奪魂狼</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pug</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pug</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">巴哥犬</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">巴哥犬</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Punisher</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Punisher</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">惩戒者</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">懲戒者</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PurpleScarab</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PurpleScarab</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">紫圣甲虫</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">紫聖甲蟲</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuickEnemy</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuickEnemy</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">快速怪</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">快速怪</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ram</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ram</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公羊</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公羊</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rat</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rat</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老鼠</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老鼠</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RatKing</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RatKing</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鼠王</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鼠王</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedScorpion</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedScorpion</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">红蝎</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">紅蠍</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rooster</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rooster</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公鸡</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公雞</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoyalBoar</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoyalBoar</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皇家野猪</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">皇家野豬</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SabretoothTiger</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SabretoothTiger</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">剑齿虎</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">劍齒虎</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scarab</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scarab</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">圣甲虫</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖甲蟲</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ScarabMounted</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ScarabMounted</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骑乘圣甲虫</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">騎乘聖甲蟲</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShardLizard</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShardLizard</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碎片蜥蜴</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碎片蜥蜴</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheep</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheep</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">绵羊</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">綿羊</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SlugQueen</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SlugQueen</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蛞蝓女王</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蛞蝓女王</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StrongEnemy</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StrongEnemy</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">强敌</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">強敵</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swine</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swine</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">壮猪</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">壯豬</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiger</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiger</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老虎</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老虎</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TreasureChest</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TreasureChest</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宝箱</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寶箱</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troll</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troll</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">巨魔</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">巨魔</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turkey</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turkey</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火鸡</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火雞</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VolcanoParasite</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VolcanoParasite</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">熔岩寄生体</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">熔岩寄生體</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warg</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warg</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">座狼</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">座狼</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wasp</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wasp</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄蜂</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃蜂</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Watchdog</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Watchdog</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看门犬</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看門犬</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WhiteWolf</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WhiteWolf</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白狼</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白狼</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WildGoat</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WildGoat</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">野山羊</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">野山羊</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WildRooster</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WildRooster</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">野公鸡</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">野公雞</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterBear</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterBear</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬熊</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬熊</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterBoar</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterBoar</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬野猪</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬野豬</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterOgre</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterOgre</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬食人魔</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬食人魔</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterWarg</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterWarg</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬座狼</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬座狼</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterWolfTypeA</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterWolfTypeA</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬狼·甲</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬狼·甲</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterWolfTypeB</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WinterWolfTypeB</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬狼·乙</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬狼·乙</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wolf</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wolf</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狼</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狼</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WolfHound</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WolfHound</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狼犬</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狼犬</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WolfMounfed</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WolfMounfed</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狼骑</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狼騎</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zombie</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zombie</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">丧尸</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">喪屍</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怪物名（关卡详情的"本关出现怪物"列表）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Config/Datas/Localization.xlsx
+++ b/Luban/Config/Datas/Localization.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F354"/>
+  <dimension ref="A1:F355"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9630,6 +9630,33 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Menu</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Menu</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">菜单</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">選單</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUD 右上角暂停菜单按钮 / 暂停菜单（未暂停时）标题</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Config/Datas/Localization.xlsx
+++ b/Luban/Config/Datas/Localization.xlsx
@@ -9633,27 +9633,27 @@
     <row r="355">
       <c r="B355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Menu</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Menu</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">菜单</t>
+          <t>菜单</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">選單</t>
+          <t>選單</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUD 右上角暂停菜单按钮 / 暂停菜单（未暂停时）标题</t>
+          <t>HUD 右上角暂停菜单按钮 / 暂停菜单（未暂停时）标题</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Localization.xlsx
+++ b/Luban/Config/Datas/Localization.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Localization" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>

--- a/Luban/Config/Datas/Localization.xlsx
+++ b/Luban/Config/Datas/Localization.xlsx
@@ -1039,77 +1039,9 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Volume {0}%</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Volume {0}%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>音量 {0}%</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>音量 {0}%</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>占位符 {0} 保留</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Mute</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Mute</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>静音</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>靜音</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Unmute</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Unmute</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>取消静音</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>取消靜音</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
@@ -4338,60 +4270,8 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Volume +</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Volume +</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>音量 ＋</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>音量 ＋</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>设置音量加</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Volume -</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Volume -</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>音量 −</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>音量 −</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>设置音量减</t>
-        </is>
-      </c>
-    </row>
+    <row r="159"/>
+    <row r="160"/>
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>

--- a/Luban/Config/Datas/Localization.xlsx
+++ b/Luban/Config/Datas/Localization.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Localization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F384"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9537,6 +9537,789 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>护甲减伤</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>護甲減傷</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/UI/MonsterCodexView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>属性比较</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>屬性比較</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Editor/TacticalForgePrefabBuilder.cs / UI state labels</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Config load failed, retrying...</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Config load failed, retrying...</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>配置读取失败，正在重试…</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>設定讀取失敗，正在重試…</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/Launcher.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Configured variants: {0}</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Configured variants: {0}</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>配置变体：{0}</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>設定變體：{0}</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Editor/TacticalForgePrefabBuilder.cs / UI state labels; Assets/Scripts/UI/MonsterCodexView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>金币奖励</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>金幣獎勵</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/UI/MonsterCodexView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Leave this battle?</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Leave this battle?</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>返回选关？只保留最后成功保存的波次检查点。</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>返回選關？只保留最後成功儲存的波次檢查點。</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/UI/PauseView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Monster Codex</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Monster Codex</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>怪物图鉴</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>怪物圖鑑</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Editor/TacticalForgePrefabBuilder.cs / UI state labels; Assets/Scripts/UI/MonsterCodexView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>More</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>More</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>更多</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>更多</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/UI/TowerActionMenu.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>射程范围</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>射程範圍</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Editor/TacticalForgePrefabBuilder.cs / UI state labels; Assets/Scripts/UI/TowerInfoView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Restart this level?</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Restart this level?</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>从头重新挑战本关？当前战斗将重新开始。</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>從頭重新挑戰本關？目前戰鬥將重新開始。</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/UI/LevelDetailView.cs; Assets/Scripts/UI/PauseView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Save reset failed</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Save reset failed</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>存档重置失败，请重试。</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>存檔重設失敗，請重試。</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/UI/SettingView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Saving...</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Saving...</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>正在保存…</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>正在儲存…</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/UI/LevelClearView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>移动速度</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>移動速度</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/UI/MonsterCodexView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>内容暂不可用</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>內容暫時無法使用</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Scripts/UI/MonsterCodexView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>View Briefing</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>View Briefing</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>查看战前简报</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>查看戰前簡報</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Editor/TacticalForgePrefabBuilder.cs / UI state labels</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>View Details</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>View Details</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>查看详情</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>查看詳情</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Tactical Forge UI 2026-10-26 | Assets/Editor/TacticalForgePrefabBuilder.cs / UI state labels; Assets/Scripts/UI/MonsterCodexView.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Tower description: normal</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Fast single-target attacks. Upgrade to increase damage, range and attack speed.</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>快速攻击单个目标。升级可提高伤害、射程与攻击频率。</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>快速攻擊單一目標。升級可提高傷害、射程與攻擊頻率。</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>UI quality fixes 2026-10-26 | TowerPresentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Tower description: blast</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Area damage against groups. Upgrade to increase damage and reach.</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>范围伤害，适合对付密集敌群。升级可提高伤害与射程。</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>範圍傷害，適合對付密集敵群。升級可提高傷害與射程。</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>UI quality fixes 2026-10-26 | TowerPresentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Tower description: slow</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Slows enemies in range. Upgrade to strengthen the slow and widen coverage.</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>持续减速范围内的敌人。升级可加强减速并扩大覆盖范围。</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>持續減速範圍內的敵人。升級可加強減速並擴大覆蓋範圍。</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>UI quality fixes 2026-10-26 | TowerPresentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Tower level upgrade: {0} → {1}</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Level {0} → {1}</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>等级 {0} → {1}</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>等級 {0} → {1}</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>UI quality fixes 2026-10-26 | TowerPresentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Damage upgrade: {0:0.#} → {1:0.#} · DPS {2:0.#} → {3:0.#}</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Damage {0:0.#} → {1:0.#} · DPS {2:0.#} → {3:0.#}</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>伤害 {0:0.#} → {1:0.#} · DPS {2:0.#} → {3:0.#}</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>傷害 {0:0.#} → {1:0.#} · DPS {2:0.#} → {3:0.#}</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>UI quality fixes 2026-10-26 | TowerPresentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Range upgrade: {0:0.##} → {1:0.##}</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Range {0:0.##} → {1:0.##} tiles</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>射程 {0:0.##} → {1:0.##} 格</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>射程 {0:0.##} → {1:0.##} 格</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>UI quality fixes 2026-10-26 | TowerPresentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Attack interval upgrade: {0:0.00}s → {1:0.00}s</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Attack interval {0:0.00}s → {1:0.00}s</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>攻击间隔 {0:0.00}秒 → {1:0.00}秒</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>攻擊間隔 {0:0.00}秒 → {1:0.00}秒</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>UI quality fixes 2026-10-26 | TowerPresentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Slow upgrade: {0:P0} → {1:P0}</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Slow {0:P0} → {1:P0}</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>减速 {0:P0} → {1:P0}</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>減速 {0:P0} → {1:P0}</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>UI quality fixes 2026-10-26 | TowerPresentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Aura refresh upgrade: {0:0.00}s → {1:0.00}s</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Aura refresh {0:0.00}s → {1:0.00}s</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>光环刷新 {0:0.00}秒 → {1:0.00}秒</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>光環刷新 {0:0.00}秒 → {1:0.00}秒</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>UI quality fixes 2026-10-26 | TowerPresentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Master Volume</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Master Volume</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>总音量</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>總音量</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Audio settings 2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Music Volume</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Music Volume</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>音乐音量</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>音樂音量</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Audio settings 2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>SFX Volume</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>SFX Volume</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>音效音量</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>音效音量</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Audio settings 2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Mute</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Mute</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>静音</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>靜音</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Audio settings 2026-10-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
